--- a/tests/Verification/sweep_results.xlsx
+++ b/tests/Verification/sweep_results.xlsx
@@ -10,7 +10,7 @@
     <sheet name="sweep_results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'sweep_results'!$A$1:$L$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'sweep_results'!$A$1:$L$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,19 +506,19 @@
         <v>2000</v>
       </c>
       <c r="G2" t="n">
-        <v>864.1017036729935</v>
+        <v>839.7471339698693</v>
       </c>
       <c r="H2" t="n">
-        <v>171.4912541368129</v>
+        <v>155.5153034782925</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0454491500696584</v>
+        <v>0.03192531252004318</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05906400982731321</v>
+        <v>0.03738647718325918</v>
       </c>
       <c r="K2" t="n">
-        <v>1.744278628440476e-06</v>
+        <v>6.98895314141263e-07</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -527,12 +527,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drag_cc_equal_area.toml</t>
+          <t>case_cc_equal_area_ar05_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Case CC Equal Area | No Refueling | AR 1.0</t>
+          <t>Case CC Equal Area | No Refueling | AR 0.5 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C3" t="b">
@@ -550,19 +550,19 @@
         <v>2000</v>
       </c>
       <c r="G3" t="n">
-        <v>864.1017036729935</v>
+        <v>871.7274683547428</v>
       </c>
       <c r="H3" t="n">
-        <v>171.4912541368129</v>
+        <v>173.8567371721308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0454491500696584</v>
+        <v>0.04397996942198748</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05906400982731321</v>
+        <v>0.05638592585981008</v>
       </c>
       <c r="K3" t="n">
-        <v>1.744278628440476e-06</v>
+        <v>1.589686317533999e-06</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>drag_cc_equal_area_ar05.toml</t>
+          <t>case_cc_equal_area_ar05_free_intake.toml</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Case CC Equal Area | No Refueling | AR 0.5</t>
+          <t>Case CC Equal Area | No Refueling | AR 0.5 | Free Intake</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -594,19 +594,19 @@
         <v>2000</v>
       </c>
       <c r="G4" t="n">
-        <v>871.7274683547428</v>
+        <v>865.0755515486198</v>
       </c>
       <c r="H4" t="n">
-        <v>173.8567371721308</v>
+        <v>180.6976158718362</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04397996942198748</v>
+        <v>0.03193529196355344</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05638592585981008</v>
+        <v>0.03738647893448457</v>
       </c>
       <c r="K4" t="n">
-        <v>1.589686317534e-06</v>
+        <v>6.988744165518767e-07</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -615,12 +615,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>drag_cc_equal_area_ar2.toml</t>
+          <t>case_cc_equal_area_ar05_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Case CC Equal Area | No Refueling | AR 2.0</t>
+          <t>Case CC Equal Area | No Refueling | AR 0.5 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -632,25 +632,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>2000</v>
       </c>
       <c r="G5" t="n">
-        <v>853.4</v>
+        <v>844.1238334481108</v>
       </c>
       <c r="H5" t="n">
-        <v>170.9671417968099</v>
+        <v>158.845584180278</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04578126494717502</v>
+        <v>0.03192678452722016</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05968401857694965</v>
+        <v>0.03738647683623175</v>
       </c>
       <c r="K5" t="n">
-        <v>1.781091036746835e-06</v>
+        <v>6.988982468477042e-07</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -659,12 +659,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drag_cc_equal_area_refuel_on.toml</t>
+          <t>case_cc_equal_area_ar2_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Case CC Equal Area | Refueling | AR 1.0</t>
+          <t>Case CC Equal Area | No Refueling | AR 2.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -676,39 +676,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>2961.385060491992</v>
+        <v>2000</v>
       </c>
       <c r="G6" t="n">
-        <v>881.7612382154621</v>
+        <v>853.4</v>
       </c>
       <c r="H6" t="n">
-        <v>203.2504430978224</v>
+        <v>170.9671417968099</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01683907896389231</v>
+        <v>0.04578126494717502</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0213757225517834</v>
+        <v>0.05968401857694965</v>
       </c>
       <c r="K6" t="n">
-        <v>2.284594780690469e-07</v>
+        <v>1.781091036746835e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>3.541620099781847e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drag_cc_equal_area_refuel_on_ar05.toml</t>
+          <t>case_cc_equal_area_ar2_free_intake.toml</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Case CC Equal Area | Refueling | AR 0.5</t>
+          <t>Case CC Equal Area | No Refueling | AR 2.0 | Free Intake</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -720,39 +720,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>2822.401574953833</v>
+        <v>2000</v>
       </c>
       <c r="G7" t="n">
-        <v>886.8340365941592</v>
+        <v>848.2079680644862</v>
       </c>
       <c r="H7" t="n">
-        <v>208.4364509209746</v>
+        <v>179.1476323238561</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01516263263206159</v>
+        <v>0.03193465073604138</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01904185575990386</v>
+        <v>0.03738647891547194</v>
       </c>
       <c r="K7" t="n">
-        <v>1.81297339789771e-07</v>
+        <v>6.988745876279206e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.170969551317487e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drag_cc_equal_area_refuel_on_ar2.toml</t>
+          <t>case_cc_equal_area_ar2_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Case CC Equal Area | Refueling | AR 2.0</t>
+          <t>Case CC Equal Area | No Refueling | AR 2.0 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C8" t="b">
@@ -764,39 +764,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>3008.07590871194</v>
+        <v>2000</v>
       </c>
       <c r="G8" t="n">
-        <v>871.8344354000061</v>
+        <v>834.894025176086</v>
       </c>
       <c r="H8" t="n">
-        <v>201.7073747582191</v>
+        <v>154.7868190478547</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01746142695656568</v>
+        <v>0.03192142150560641</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02221895816572492</v>
+        <v>0.03738648863661808</v>
       </c>
       <c r="K8" t="n">
-        <v>2.468395858960102e-07</v>
+        <v>6.987573297061768e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>3.640776314963104e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>drag_cc_intake_gt_body_wake_split.toml</t>
+          <t>case_cc_equal_area_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 1.0</t>
+          <t>Case CC Equal Area | No Refueling | AR 1.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C9" t="b">
@@ -835,12 +835,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>drag_cc_intake_gt_body_wake_split_ar05.toml</t>
+          <t>case_cc_equal_area_free_intake.toml</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 0.5</t>
+          <t>Case CC Equal Area | No Refueling | AR 1.0 | Free Intake</t>
         </is>
       </c>
       <c r="C10" t="b">
@@ -858,19 +858,19 @@
         <v>2000</v>
       </c>
       <c r="G10" t="n">
-        <v>871.7274683547428</v>
+        <v>856.8876078308514</v>
       </c>
       <c r="H10" t="n">
-        <v>173.8567371721308</v>
+        <v>175.0343139529288</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04397996942198748</v>
+        <v>0.03193293415333311</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05638592585981008</v>
+        <v>0.03738647893594604</v>
       </c>
       <c r="K10" t="n">
-        <v>1.589686317534e-06</v>
+        <v>6.988744036139689e-07</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -879,12 +879,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>drag_cc_intake_gt_body_wake_split_ar2.toml</t>
+          <t>case_cc_equal_area_refuel_on_ar05_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 2.0</t>
+          <t>Case CC Equal Area | Refueling | AR 0.5 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C11" t="b">
@@ -896,39 +896,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>2000</v>
+        <v>3324.179630465645</v>
       </c>
       <c r="G11" t="n">
-        <v>853.4</v>
+        <v>896.0511206410331</v>
       </c>
       <c r="H11" t="n">
-        <v>170.9671417968099</v>
+        <v>193.1252871228226</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04578126494717502</v>
+        <v>0.02483915422175418</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05968401857694965</v>
+        <v>0.03109253018360645</v>
       </c>
       <c r="K11" t="n">
-        <v>1.781091036746835e-06</v>
+        <v>4.833749164648803e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.191084364061451e-07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>drag_cc_intake_gt_body_wake_split_refuel_on.toml</t>
+          <t>case_cc_equal_area_refuel_on_ar05_free_intake.toml</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 1.0</t>
+          <t>Case CC Equal Area | Refueling | AR 0.5 | Free Intake</t>
         </is>
       </c>
       <c r="C12" t="b">
@@ -940,39 +940,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>2961.385060491992</v>
+        <v>3801.67309429044</v>
       </c>
       <c r="G12" t="n">
-        <v>881.7612382154621</v>
+        <v>916.020169694317</v>
       </c>
       <c r="H12" t="n">
-        <v>203.2504430978224</v>
+        <v>199.7652375221316</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01683907896389231</v>
+        <v>0.02888283969021711</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0213757225517834</v>
+        <v>0.03738647769279124</v>
       </c>
       <c r="K12" t="n">
-        <v>2.284594780690469e-07</v>
+        <v>6.98883932699722e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>3.541620099781847e-07</v>
+        <v>3.929714562668722e-07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>drag_cc_intake_gt_body_wake_split_refuel_on_ar05.toml</t>
+          <t>case_cc_equal_area_refuel_on_ar05_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 0.5</t>
+          <t>Case CC Equal Area | Refueling | AR 0.5 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C13" t="b">
@@ -984,39 +984,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>2822.401574953833</v>
+        <v>3824.408899771404</v>
       </c>
       <c r="G13" t="n">
-        <v>886.8340365941592</v>
+        <v>948.1524120256875</v>
       </c>
       <c r="H13" t="n">
-        <v>208.4364509209746</v>
+        <v>205.8108490536011</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01516263263206159</v>
+        <v>0.02877922452486226</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01904185575990386</v>
+        <v>0.0373864784905517</v>
       </c>
       <c r="K13" t="n">
-        <v>1.81297339789771e-07</v>
+        <v>6.988776934504182e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>3.170969551317487e-07</v>
+        <v>4.067561172595854e-07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>drag_cc_intake_gt_body_wake_split_refuel_on_ar2.toml</t>
+          <t>case_cc_equal_area_refuel_on_ar2_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 2.0</t>
+          <t>Case CC Equal Area | Refueling | AR 2.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C14" t="b">
@@ -1031,36 +1031,36 @@
         <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>3008.07590871194</v>
+        <v>3509.762041044328</v>
       </c>
       <c r="G14" t="n">
-        <v>871.8344354000061</v>
+        <v>881.0498309241132</v>
       </c>
       <c r="H14" t="n">
-        <v>201.7073747582191</v>
+        <v>189.177891274844</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01746142695656568</v>
+        <v>0.02672191303095112</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02221895816572492</v>
+        <v>0.0338538247218817</v>
       </c>
       <c r="K14" t="n">
-        <v>2.468395858960102e-07</v>
+        <v>5.730444053566038e-07</v>
       </c>
       <c r="L14" t="n">
-        <v>3.640776314963104e-07</v>
+        <v>3.419061624214348e-07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>drag_cr_equal_area.toml</t>
+          <t>case_cc_equal_area_refuel_on_ar2_free_intake.toml</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Case CR Equal Area | No Refueling | AR 1.0</t>
+          <t>Case CC Equal Area | Refueling | AR 2.0 | Free Intake</t>
         </is>
       </c>
       <c r="C15" t="b">
@@ -1072,39 +1072,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
-        <v>2000</v>
+        <v>3783.578283818953</v>
       </c>
       <c r="G15" t="n">
-        <v>865.860506681208</v>
+        <v>890.4393038844235</v>
       </c>
       <c r="H15" t="n">
-        <v>172.7526235885518</v>
+        <v>193.0230673121697</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04465957190975832</v>
+        <v>0.02896428692266793</v>
       </c>
       <c r="J15" t="n">
-        <v>0.05761200920299393</v>
+        <v>0.03738647671336936</v>
       </c>
       <c r="K15" t="n">
-        <v>1.659571802202929e-06</v>
+        <v>6.988922203295847e-07</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.81997296754795e-07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>drag_cr_equal_area_ar05.toml</t>
+          <t>case_cc_equal_area_refuel_on_ar2_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Case CR Equal Area | No Refueling | AR 0.5</t>
+          <t>Case CC Equal Area | Refueling | AR 2.0 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C16" t="b">
@@ -1116,39 +1116,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>2000</v>
+        <v>3790.659187349458</v>
       </c>
       <c r="G16" t="n">
-        <v>872.9711298886225</v>
+        <v>900.4688637196042</v>
       </c>
       <c r="H16" t="n">
-        <v>174.8621686701721</v>
+        <v>195.2708992638502</v>
       </c>
       <c r="I16" t="n">
-        <v>0.04337046152529268</v>
+        <v>0.0289318206298932</v>
       </c>
       <c r="J16" t="n">
-        <v>0.05530396684266069</v>
+        <v>0.03738647812774539</v>
       </c>
       <c r="K16" t="n">
-        <v>1.529264374267056e-06</v>
+        <v>6.988807828974657e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.862999248046988e-07</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>drag_cr_equal_area_ar2.toml</t>
+          <t>case_cc_equal_area_refuel_on_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Case CR Equal Area | No Refueling | AR 2.0</t>
+          <t>Case CC Equal Area | Refueling | AR 1.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C17" t="b">
@@ -1160,39 +1160,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>2000</v>
+        <v>3467.57466912328</v>
       </c>
       <c r="G17" t="n">
-        <v>855.8045669043574</v>
+        <v>891.0593574041338</v>
       </c>
       <c r="H17" t="n">
-        <v>172.1646396847524</v>
+        <v>190.020886007102</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04502592698860284</v>
+        <v>0.02624971771164347</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05828194253928824</v>
+        <v>0.03318189332031497</v>
       </c>
       <c r="K17" t="n">
-        <v>1.698392413076448e-06</v>
+        <v>5.50522821495827e-07</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.388612272925524e-07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>drag_cr_equal_area_refuel_on.toml</t>
+          <t>case_cc_equal_area_refuel_on_free_intake.toml</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Case CR Equal Area | Refueling | AR 1.0</t>
+          <t>Case CC Equal Area | Refueling | AR 1.0 | Free Intake</t>
         </is>
       </c>
       <c r="C18" t="b">
@@ -1204,39 +1204,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F18" t="n">
-        <v>2889.089770120168</v>
+        <v>3792.663037283814</v>
       </c>
       <c r="G18" t="n">
-        <v>882.1920601367585</v>
+        <v>903.2838365474086</v>
       </c>
       <c r="H18" t="n">
-        <v>205.8270679987491</v>
+        <v>194.6228388347455</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01600680493669966</v>
+        <v>0.02892221038141478</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02020142598782352</v>
+        <v>0.03738647728673886</v>
       </c>
       <c r="K18" t="n">
-        <v>2.040500870819826e-07</v>
+        <v>6.988874960912534e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>3.347587899874135e-07</v>
+        <v>3.875075908212349e-07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>drag_cr_equal_area_refuel_on_ar05.toml</t>
+          <t>case_cc_equal_area_refuel_on_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Case CR Equal Area | Refueling | AR 0.5</t>
+          <t>Case CC Equal Area | Refueling | AR 1.0 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C19" t="b">
@@ -1248,39 +1248,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F19" t="n">
-        <v>2769.91453102626</v>
+        <v>3803.373213675648</v>
       </c>
       <c r="G19" t="n">
-        <v>887.1135716782305</v>
+        <v>918.4334003824322</v>
       </c>
       <c r="H19" t="n">
-        <v>210.6744704357304</v>
+        <v>197.6456511288762</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01450783956879834</v>
+        <v>0.02887324034148687</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01813886472742431</v>
+        <v>0.0373864783449626</v>
       </c>
       <c r="K19" t="n">
-        <v>1.645103903600165e-07</v>
+        <v>6.988789942371758e-07</v>
       </c>
       <c r="L19" t="n">
-        <v>3.020755471270395e-07</v>
+        <v>3.940067062318258e-07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>drag_cr_equal_area_refuel_on_ar2.toml</t>
+          <t>case_cc_equal_area_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Case CR Equal Area | Refueling | AR 2.0</t>
+          <t>Case CC Equal Area | No Refueling | AR 1.0 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C20" t="b">
@@ -1292,39 +1292,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>2935.890174441796</v>
+        <v>2000</v>
       </c>
       <c r="G20" t="n">
-        <v>872.9957898000555</v>
+        <v>839.7471339698693</v>
       </c>
       <c r="H20" t="n">
-        <v>204.1320168780207</v>
+        <v>155.5153034782925</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01664329636326498</v>
+        <v>0.03192531252004318</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02105928025534604</v>
+        <v>0.03738647718325918</v>
       </c>
       <c r="K20" t="n">
-        <v>2.217482926820175e-07</v>
+        <v>6.98895314141263e-07</v>
       </c>
       <c r="L20" t="n">
-        <v>3.454227072532414e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>drag_cr_intake_gt_body_wake_split.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_ar05_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 1.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C21" t="b">
@@ -1342,19 +1342,19 @@
         <v>2000</v>
       </c>
       <c r="G21" t="n">
-        <v>865.860506681208</v>
+        <v>871.7274683547428</v>
       </c>
       <c r="H21" t="n">
-        <v>172.7526235885518</v>
+        <v>173.8567371721308</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04465957190975832</v>
+        <v>0.04397996942198748</v>
       </c>
       <c r="J21" t="n">
-        <v>0.05761200920299393</v>
+        <v>0.05638592585981008</v>
       </c>
       <c r="K21" t="n">
-        <v>1.659571802202929e-06</v>
+        <v>1.589686317533999e-06</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1363,12 +1363,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>drag_cr_intake_gt_body_wake_split_ar05.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_ar05_free_intake.toml</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 0.5</t>
+          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Free Intake</t>
         </is>
       </c>
       <c r="C22" t="b">
@@ -1386,19 +1386,19 @@
         <v>2000</v>
       </c>
       <c r="G22" t="n">
-        <v>872.9711298886225</v>
+        <v>865.0755515486198</v>
       </c>
       <c r="H22" t="n">
-        <v>174.8621686701721</v>
+        <v>180.6976158718362</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04337046152529268</v>
+        <v>0.03193529196355344</v>
       </c>
       <c r="J22" t="n">
-        <v>0.05530396684266069</v>
+        <v>0.03738647893448457</v>
       </c>
       <c r="K22" t="n">
-        <v>1.529264374267056e-06</v>
+        <v>6.988744165518767e-07</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1407,12 +1407,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>drag_cr_intake_gt_body_wake_split_ar2.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_ar05_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 2.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C23" t="b">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
         <v>2000</v>
       </c>
       <c r="G23" t="n">
-        <v>855.8045669043574</v>
+        <v>844.1238334481108</v>
       </c>
       <c r="H23" t="n">
-        <v>172.1646396847524</v>
+        <v>158.845584180278</v>
       </c>
       <c r="I23" t="n">
-        <v>0.04502592698860284</v>
+        <v>0.03192678452722016</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05828194253928824</v>
+        <v>0.03738647683623175</v>
       </c>
       <c r="K23" t="n">
-        <v>1.698392413076448e-06</v>
+        <v>6.988982468477042e-07</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1451,12 +1451,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>drag_cr_intake_gt_body_wake_split_refuel_on.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_ar2_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 1.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C24" t="b">
@@ -1468,39 +1468,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>2889.089770120168</v>
+        <v>2000</v>
       </c>
       <c r="G24" t="n">
-        <v>882.1920601367585</v>
+        <v>853.4</v>
       </c>
       <c r="H24" t="n">
-        <v>205.8270679987491</v>
+        <v>170.9671417968099</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01600680493669966</v>
+        <v>0.04578126494717502</v>
       </c>
       <c r="J24" t="n">
-        <v>0.02020142598782352</v>
+        <v>0.05968401857694965</v>
       </c>
       <c r="K24" t="n">
-        <v>2.040500870819826e-07</v>
+        <v>1.781091036746835e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>3.347587899874135e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>drag_cr_intake_gt_body_wake_split_refuel_on_ar05.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_ar2_free_intake.toml</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 0.5</t>
+          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Free Intake</t>
         </is>
       </c>
       <c r="C25" t="b">
@@ -1512,39 +1512,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>2769.91453102626</v>
+        <v>2000</v>
       </c>
       <c r="G25" t="n">
-        <v>887.1135716782305</v>
+        <v>848.2079680644862</v>
       </c>
       <c r="H25" t="n">
-        <v>210.6744704357304</v>
+        <v>179.1476323238561</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01450783956879834</v>
+        <v>0.03193465073604138</v>
       </c>
       <c r="J25" t="n">
-        <v>0.01813886472742431</v>
+        <v>0.03738647891547194</v>
       </c>
       <c r="K25" t="n">
-        <v>1.645103903600165e-07</v>
+        <v>6.988745876279206e-07</v>
       </c>
       <c r="L25" t="n">
-        <v>3.020755471270395e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>drag_cr_intake_gt_body_wake_split_refuel_on_ar2.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_ar2_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 2.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C26" t="b">
@@ -1556,39 +1556,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>2935.890174441796</v>
+        <v>2000</v>
       </c>
       <c r="G26" t="n">
-        <v>872.9957898000555</v>
+        <v>834.894025176086</v>
       </c>
       <c r="H26" t="n">
-        <v>204.1320168780207</v>
+        <v>154.7868190478547</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01664329636326498</v>
+        <v>0.03192142150560641</v>
       </c>
       <c r="J26" t="n">
-        <v>0.02105928025534604</v>
+        <v>0.03738648863661808</v>
       </c>
       <c r="K26" t="n">
-        <v>2.217482926820175e-07</v>
+        <v>6.987573297061768e-07</v>
       </c>
       <c r="L26" t="n">
-        <v>3.454227072532414e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>drag_rc_equal_area.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Case RC Equal Area | No Refueling | AR 1.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C27" t="b">
@@ -1606,19 +1606,19 @@
         <v>2000</v>
       </c>
       <c r="G27" t="n">
-        <v>865.3050952049298</v>
+        <v>864.1017036729935</v>
       </c>
       <c r="H27" t="n">
-        <v>172.3547806037884</v>
+        <v>171.4912541368129</v>
       </c>
       <c r="I27" t="n">
-        <v>0.04490710210813625</v>
+        <v>0.0454491500696584</v>
       </c>
       <c r="J27" t="n">
-        <v>0.05806394767224868</v>
+        <v>0.05906400982731321</v>
       </c>
       <c r="K27" t="n">
-        <v>1.685711009642817e-06</v>
+        <v>1.744278628440476e-06</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1627,12 +1627,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>drag_rc_equal_area_ar05.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_free_intake.toml</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Case RC Equal Area | No Refueling | AR 0.5</t>
+          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Free Intake</t>
         </is>
       </c>
       <c r="C28" t="b">
@@ -1650,19 +1650,19 @@
         <v>2000</v>
       </c>
       <c r="G28" t="n">
-        <v>872.5783946673973</v>
+        <v>856.8876078308514</v>
       </c>
       <c r="H28" t="n">
-        <v>174.5450461356472</v>
+        <v>175.0343139529288</v>
       </c>
       <c r="I28" t="n">
-        <v>0.04356174661737805</v>
+        <v>0.03193293415333311</v>
       </c>
       <c r="J28" t="n">
-        <v>0.05564177406660649</v>
+        <v>0.03738647893594604</v>
       </c>
       <c r="K28" t="n">
-        <v>1.548003510639641e-06</v>
+        <v>6.988744036139689e-07</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1671,12 +1671,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>drag_rc_equal_area_ar2.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_refuel_on_ar05_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Case RC Equal Area | No Refueling | AR 2.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 0.5 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C29" t="b">
@@ -1688,39 +1688,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>2000</v>
+        <v>3324.179630465645</v>
       </c>
       <c r="G29" t="n">
-        <v>855.0190964619071</v>
+        <v>896.0511206410331</v>
       </c>
       <c r="H29" t="n">
-        <v>171.7827566487942</v>
+        <v>193.1252871228226</v>
       </c>
       <c r="I29" t="n">
-        <v>0.04526543915740137</v>
+        <v>0.02483915422175418</v>
       </c>
       <c r="J29" t="n">
-        <v>0.05872344387826645</v>
+        <v>0.03109253018360645</v>
       </c>
       <c r="K29" t="n">
-        <v>1.724221430461955e-06</v>
+        <v>4.833749164648803e-07</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.191084364061451e-07</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>drag_rc_equal_area_refuel_on.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_refuel_on_ar05_free_intake.toml</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Case RC Equal Area | Refueling | AR 1.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 0.5 | Free Intake</t>
         </is>
       </c>
       <c r="C30" t="b">
@@ -1732,39 +1732,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F30" t="n">
-        <v>2911.511460890878</v>
+        <v>3801.67309429044</v>
       </c>
       <c r="G30" t="n">
-        <v>882.0485092550928</v>
+        <v>916.020169694317</v>
       </c>
       <c r="H30" t="n">
-        <v>205.0019582723214</v>
+        <v>199.7652375221316</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01626893430528045</v>
+        <v>0.02888283969021711</v>
       </c>
       <c r="J30" t="n">
-        <v>0.02056960429097102</v>
+        <v>0.03738647769279124</v>
       </c>
       <c r="K30" t="n">
-        <v>2.115558256129421e-07</v>
+        <v>6.98883932699722e-07</v>
       </c>
       <c r="L30" t="n">
-        <v>3.408411124511618e-07</v>
+        <v>3.929714562668722e-07</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>drag_rc_equal_area_refuel_on_ar05.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_refuel_on_ar05_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Case RC Equal Area | Refueling | AR 0.5</t>
+          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 0.5 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C31" t="b">
@@ -1776,39 +1776,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F31" t="n">
-        <v>2786.240184370984</v>
+        <v>3824.408899771404</v>
       </c>
       <c r="G31" t="n">
-        <v>887.0207198762693</v>
+        <v>948.1524120256875</v>
       </c>
       <c r="H31" t="n">
-        <v>209.9592759473128</v>
+        <v>205.8108490536011</v>
       </c>
       <c r="I31" t="n">
-        <v>0.01471405240259267</v>
+        <v>0.02877922452486226</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01842227906878167</v>
+        <v>0.0373864784905517</v>
       </c>
       <c r="K31" t="n">
-        <v>1.696911271908008e-07</v>
+        <v>6.988776934504182e-07</v>
       </c>
       <c r="L31" t="n">
-        <v>3.067885322146911e-07</v>
+        <v>4.067561172595854e-07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>drag_rc_equal_area_refuel_on_ar2.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_refuel_on_ar2_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Case RC Equal Area | Refueling | AR 2.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 2.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C32" t="b">
@@ -1820,39 +1820,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F32" t="n">
-        <v>2958.303640289227</v>
+        <v>3509.762041044328</v>
       </c>
       <c r="G32" t="n">
-        <v>872.6220288698651</v>
+        <v>881.0498309241132</v>
       </c>
       <c r="H32" t="n">
-        <v>203.3558731814037</v>
+        <v>189.177891274844</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01690110301315047</v>
+        <v>0.02672191303095112</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02142310706013095</v>
+        <v>0.0338538247218817</v>
       </c>
       <c r="K32" t="n">
-        <v>2.294766896624995e-07</v>
+        <v>5.730444053566038e-07</v>
       </c>
       <c r="L32" t="n">
-        <v>3.512773867745341e-07</v>
+        <v>3.419061624214348e-07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>drag_rc_intake_gt_body_wake_split.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_refuel_on_ar2_free_intake.toml</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 1.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 2.0 | Free Intake</t>
         </is>
       </c>
       <c r="C33" t="b">
@@ -1864,39 +1864,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F33" t="n">
-        <v>2000</v>
+        <v>3783.578283818953</v>
       </c>
       <c r="G33" t="n">
-        <v>865.3050952049298</v>
+        <v>890.4393038844235</v>
       </c>
       <c r="H33" t="n">
-        <v>172.3547806037884</v>
+        <v>193.0230673121697</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04490710210813625</v>
+        <v>0.02896428692266793</v>
       </c>
       <c r="J33" t="n">
-        <v>0.05806394767224868</v>
+        <v>0.03738647671336936</v>
       </c>
       <c r="K33" t="n">
-        <v>1.685711009642817e-06</v>
+        <v>6.988922203295847e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.81997296754795e-07</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>drag_rc_intake_gt_body_wake_split_ar05.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_refuel_on_ar2_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 0.5</t>
+          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 2.0 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C34" t="b">
@@ -1908,39 +1908,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F34" t="n">
-        <v>2000</v>
+        <v>3790.659187349458</v>
       </c>
       <c r="G34" t="n">
-        <v>872.5783946673973</v>
+        <v>900.4688637196042</v>
       </c>
       <c r="H34" t="n">
-        <v>174.5450461356472</v>
+        <v>195.2708992638502</v>
       </c>
       <c r="I34" t="n">
-        <v>0.04356174661737805</v>
+        <v>0.0289318206298932</v>
       </c>
       <c r="J34" t="n">
-        <v>0.05564177406660649</v>
+        <v>0.03738647812774539</v>
       </c>
       <c r="K34" t="n">
-        <v>1.548003510639641e-06</v>
+        <v>6.988807828974657e-07</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.862999248046988e-07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>drag_rc_intake_gt_body_wake_split_ar2.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_refuel_on_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 2.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 1.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C35" t="b">
@@ -1952,39 +1952,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F35" t="n">
-        <v>2000</v>
+        <v>3467.57466912328</v>
       </c>
       <c r="G35" t="n">
-        <v>855.0190964619071</v>
+        <v>891.0593574041338</v>
       </c>
       <c r="H35" t="n">
-        <v>171.7827566487942</v>
+        <v>190.020886007102</v>
       </c>
       <c r="I35" t="n">
-        <v>0.04526543915740137</v>
+        <v>0.02624971771164347</v>
       </c>
       <c r="J35" t="n">
-        <v>0.05872344387826645</v>
+        <v>0.03318189332031497</v>
       </c>
       <c r="K35" t="n">
-        <v>1.724221430461955e-06</v>
+        <v>5.50522821495827e-07</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.388612272925524e-07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>drag_rc_intake_gt_body_wake_split_refuel_on.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_refuel_on_free_intake.toml</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 1.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 1.0 | Free Intake</t>
         </is>
       </c>
       <c r="C36" t="b">
@@ -1996,39 +1996,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F36" t="n">
-        <v>2911.511460890878</v>
+        <v>3792.663037283814</v>
       </c>
       <c r="G36" t="n">
-        <v>882.0485092550928</v>
+        <v>903.2838365474086</v>
       </c>
       <c r="H36" t="n">
-        <v>205.0019582723214</v>
+        <v>194.6228388347455</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01626893430528045</v>
+        <v>0.02892221038141478</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02056960429097102</v>
+        <v>0.03738647728673886</v>
       </c>
       <c r="K36" t="n">
-        <v>2.115558256129421e-07</v>
+        <v>6.988874960912534e-07</v>
       </c>
       <c r="L36" t="n">
-        <v>3.408411124511618e-07</v>
+        <v>3.875075908212349e-07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>drag_rc_intake_gt_body_wake_split_refuel_on_ar05.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_refuel_on_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 0.5</t>
+          <t>Case CC Intake&gt;Body Wake Split | Refueling | AR 1.0 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C37" t="b">
@@ -2040,39 +2040,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F37" t="n">
-        <v>2786.240184370984</v>
+        <v>3803.373213675648</v>
       </c>
       <c r="G37" t="n">
-        <v>887.0207198762693</v>
+        <v>918.4334003824322</v>
       </c>
       <c r="H37" t="n">
-        <v>209.9592759473128</v>
+        <v>197.6456511288762</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01471405240259267</v>
+        <v>0.02887324034148687</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01842227906878167</v>
+        <v>0.0373864783449626</v>
       </c>
       <c r="K37" t="n">
-        <v>1.696911271908008e-07</v>
+        <v>6.988789942371758e-07</v>
       </c>
       <c r="L37" t="n">
-        <v>3.067885322146911e-07</v>
+        <v>3.940067062318258e-07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>drag_rc_intake_gt_body_wake_split_refuel_on_ar2.toml</t>
+          <t>case_cc_intake_gt_body_wake_split_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 2.0</t>
+          <t>Case CC Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C38" t="b">
@@ -2084,39 +2084,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>2958.303640289227</v>
+        <v>2000</v>
       </c>
       <c r="G38" t="n">
-        <v>872.6220288698651</v>
+        <v>839.7471339698693</v>
       </c>
       <c r="H38" t="n">
-        <v>203.3558731814037</v>
+        <v>155.5153034782925</v>
       </c>
       <c r="I38" t="n">
-        <v>0.01690110301315047</v>
+        <v>0.03192531252004318</v>
       </c>
       <c r="J38" t="n">
-        <v>0.02142310706013095</v>
+        <v>0.03738647718325918</v>
       </c>
       <c r="K38" t="n">
-        <v>2.294766896624995e-07</v>
+        <v>6.98895314141263e-07</v>
       </c>
       <c r="L38" t="n">
-        <v>3.512773867745341e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>drag_rr_equal_area.toml</t>
+          <t>case_cr_equal_area_ar05_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Case RR Equal Area | No Refueling | AR 1.0</t>
+          <t>Case CR Equal Area | No Refueling | AR 0.5 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C39" t="b">
@@ -2134,19 +2134,19 @@
         <v>2000</v>
       </c>
       <c r="G39" t="n">
-        <v>867.0638982131443</v>
+        <v>872.9711298886225</v>
       </c>
       <c r="H39" t="n">
-        <v>173.6130735295342</v>
+        <v>174.8621686701721</v>
       </c>
       <c r="I39" t="n">
-        <v>0.04412903231092109</v>
+        <v>0.04337046152529268</v>
       </c>
       <c r="J39" t="n">
-        <v>0.05665304087567893</v>
+        <v>0.05530396684266069</v>
       </c>
       <c r="K39" t="n">
-        <v>1.604783520230673e-06</v>
+        <v>1.529264374267057e-06</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2155,12 +2155,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>drag_rr_equal_area_ar05.toml</t>
+          <t>case_cr_equal_area_ar05_free_intake.toml</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Case RR Equal Area | No Refueling | AR 0.5</t>
+          <t>Case CR Equal Area | No Refueling | AR 0.5 | Free Intake</t>
         </is>
       </c>
       <c r="C40" t="b">
@@ -2178,19 +2178,19 @@
         <v>2000</v>
       </c>
       <c r="G40" t="n">
-        <v>873.8220562012771</v>
+        <v>865.2755014245039</v>
       </c>
       <c r="H40" t="n">
-        <v>175.5481317146771</v>
+        <v>177.0307166627742</v>
       </c>
       <c r="I40" t="n">
-        <v>0.04295978070347077</v>
+        <v>0.0319337655730393</v>
       </c>
       <c r="J40" t="n">
-        <v>0.05458398282249579</v>
+        <v>0.03738647893593702</v>
       </c>
       <c r="K40" t="n">
-        <v>1.489705590383257e-06</v>
+        <v>6.988744036968274e-07</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2199,12 +2199,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>drag_rr_equal_area_ar2.toml</t>
+          <t>case_cr_equal_area_ar05_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Case RR Equal Area | No Refueling | AR 2.0</t>
+          <t>Case CR Equal Area | No Refueling | AR 0.5 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C41" t="b">
@@ -2216,25 +2216,25 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
         <v>2000</v>
       </c>
       <c r="G41" t="n">
-        <v>857.5064195296667</v>
+        <v>845.2261755508121</v>
       </c>
       <c r="H41" t="n">
-        <v>172.9905313995028</v>
+        <v>160.3080978258472</v>
       </c>
       <c r="I41" t="n">
-        <v>0.04451225967039768</v>
+        <v>0.03192736497339169</v>
       </c>
       <c r="J41" t="n">
-        <v>0.05734442603621422</v>
+        <v>0.03738647692267338</v>
       </c>
       <c r="K41" t="n">
-        <v>1.644191598711422e-06</v>
+        <v>6.988967945556654e-07</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2243,12 +2243,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>drag_rr_equal_area_refuel_on.toml</t>
+          <t>case_cr_equal_area_ar2_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Case RR Equal Area | Refueling | AR 1.0</t>
+          <t>Case CR Equal Area | No Refueling | AR 2.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C42" t="b">
@@ -2260,39 +2260,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>2841.801523319898</v>
+        <v>2000</v>
       </c>
       <c r="G42" t="n">
-        <v>882.526821124972</v>
+        <v>855.8045669043574</v>
       </c>
       <c r="H42" t="n">
-        <v>207.6524985120866</v>
+        <v>172.1646396847524</v>
       </c>
       <c r="I42" t="n">
-        <v>0.01544121665596503</v>
+        <v>0.04502592698860284</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01941212310163828</v>
+        <v>0.05828194253928824</v>
       </c>
       <c r="K42" t="n">
-        <v>1.884194880620861e-07</v>
+        <v>1.698392413076448e-06</v>
       </c>
       <c r="L42" t="n">
-        <v>3.217316223640271e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>drag_rr_equal_area_refuel_on_ar05.toml</t>
+          <t>case_cr_equal_area_ar2_free_intake.toml</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Case RR Equal Area | Refueling | AR 0.5</t>
+          <t>Case CR Equal Area | No Refueling | AR 2.0 | Free Intake</t>
         </is>
       </c>
       <c r="C43" t="b">
@@ -2304,39 +2304,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
-        <v>2735.291596526364</v>
+        <v>2000</v>
       </c>
       <c r="G43" t="n">
-        <v>887.3285146238775</v>
+        <v>850.0595438025169</v>
       </c>
       <c r="H43" t="n">
-        <v>212.252547492157</v>
+        <v>175.421277330283</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01406261046876454</v>
+        <v>0.0319330956336888</v>
       </c>
       <c r="J43" t="n">
-        <v>0.01752994170999109</v>
+        <v>0.03738647893441586</v>
       </c>
       <c r="K43" t="n">
-        <v>1.536501574687842e-07</v>
+        <v>6.988744178633079e-07</v>
       </c>
       <c r="L43" t="n">
-        <v>2.919534843202627e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>drag_rr_equal_area_refuel_on_ar2.toml</t>
+          <t>case_cr_equal_area_ar2_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Case RR Equal Area | Refueling | AR 2.0</t>
+          <t>Case CR Equal Area | No Refueling | AR 2.0 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C44" t="b">
@@ -2348,39 +2348,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F44" t="n">
-        <v>2888.470760927617</v>
+        <v>2000</v>
       </c>
       <c r="G44" t="n">
-        <v>873.8266025004165</v>
+        <v>836.1449750313232</v>
       </c>
       <c r="H44" t="n">
-        <v>205.8473980682912</v>
+        <v>156.4511889841546</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01608674822264112</v>
+        <v>0.03192300297800277</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02027879107625374</v>
+        <v>0.03738648594599184</v>
       </c>
       <c r="K44" t="n">
-        <v>2.055986165172611e-07</v>
+        <v>6.987919589540284e-07</v>
       </c>
       <c r="L44" t="n">
-        <v>3.328351267252224e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>drag_rr_intake_gt_body_wake_split.toml</t>
+          <t>case_cr_equal_area_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 1.0</t>
+          <t>Case CR Equal Area | No Refueling | AR 1.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C45" t="b">
@@ -2398,19 +2398,19 @@
         <v>2000</v>
       </c>
       <c r="G45" t="n">
-        <v>867.0638982131443</v>
+        <v>865.860506681208</v>
       </c>
       <c r="H45" t="n">
-        <v>173.6130735295342</v>
+        <v>172.7526235885518</v>
       </c>
       <c r="I45" t="n">
-        <v>0.04412903231092109</v>
+        <v>0.04465957190975832</v>
       </c>
       <c r="J45" t="n">
-        <v>0.05665304087567893</v>
+        <v>0.05761200920299393</v>
       </c>
       <c r="K45" t="n">
-        <v>1.604783520230673e-06</v>
+        <v>1.659571802202929e-06</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2419,12 +2419,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>drag_rr_intake_gt_body_wake_split_ar05.toml</t>
+          <t>case_cr_equal_area_free_intake.toml</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 0.5</t>
+          <t>Case CR Equal Area | No Refueling | AR 1.0 | Free Intake</t>
         </is>
       </c>
       <c r="C46" t="b">
@@ -2442,19 +2442,19 @@
         <v>2000</v>
       </c>
       <c r="G46" t="n">
-        <v>873.8220562012771</v>
+        <v>858.1781206348586</v>
       </c>
       <c r="H46" t="n">
-        <v>175.5481317146771</v>
+        <v>172.6822701304747</v>
       </c>
       <c r="I46" t="n">
-        <v>0.04295978070347077</v>
+        <v>0.0319319541375369</v>
       </c>
       <c r="J46" t="n">
-        <v>0.05458398282249579</v>
+        <v>0.03738647893594608</v>
       </c>
       <c r="K46" t="n">
-        <v>1.489705590383257e-06</v>
+        <v>6.988744036136792e-07</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2463,12 +2463,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>drag_rr_intake_gt_body_wake_split_ar2.toml</t>
+          <t>case_cr_equal_area_refuel_on_ar05_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 2.0</t>
+          <t>Case CR Equal Area | Refueling | AR 0.5 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C47" t="b">
@@ -2480,39 +2480,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F47" t="n">
-        <v>2000</v>
+        <v>3268.426121747752</v>
       </c>
       <c r="G47" t="n">
-        <v>857.5064195296667</v>
+        <v>896.270654534981</v>
       </c>
       <c r="H47" t="n">
-        <v>172.9905313995028</v>
+        <v>194.4454717357742</v>
       </c>
       <c r="I47" t="n">
-        <v>0.04451225967039768</v>
+        <v>0.02427778385194725</v>
       </c>
       <c r="J47" t="n">
-        <v>0.05734442603621422</v>
+        <v>0.03026727049398047</v>
       </c>
       <c r="K47" t="n">
-        <v>1.644191598711422e-06</v>
+        <v>4.580554300394313e-07</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.106400125051643e-07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>drag_rr_intake_gt_body_wake_split_refuel_on.toml</t>
+          <t>case_cr_equal_area_refuel_on_ar05_free_intake.toml</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 1.0</t>
+          <t>Case CR Equal Area | Refueling | AR 0.5 | Free Intake</t>
         </is>
       </c>
       <c r="C48" t="b">
@@ -2524,39 +2524,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F48" t="n">
-        <v>2841.801523319898</v>
+        <v>3803.765262357243</v>
       </c>
       <c r="G48" t="n">
-        <v>882.526821124972</v>
+        <v>918.9728560919849</v>
       </c>
       <c r="H48" t="n">
-        <v>207.6524985120866</v>
+        <v>201.5727192143722</v>
       </c>
       <c r="I48" t="n">
-        <v>0.01544121665596503</v>
+        <v>0.02887418939032195</v>
       </c>
       <c r="J48" t="n">
-        <v>0.01941212310163828</v>
+        <v>0.03738647751493945</v>
       </c>
       <c r="K48" t="n">
-        <v>1.884194880620861e-07</v>
+        <v>6.988851692686321e-07</v>
       </c>
       <c r="L48" t="n">
-        <v>3.217316223640271e-07</v>
+        <v>3.942381217305791e-07</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>drag_rr_intake_gt_body_wake_split_refuel_on_ar05.toml</t>
+          <t>case_cr_equal_area_refuel_on_ar05_variable_body_ratio.toml</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 0.5</t>
+          <t>Case CR Equal Area | Refueling | AR 0.5 | Variable Body Ratio</t>
         </is>
       </c>
       <c r="C49" t="b">
@@ -2568,39 +2568,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="F49" t="n">
-        <v>2735.291596526364</v>
+        <v>3833.119900767944</v>
       </c>
       <c r="G49" t="n">
-        <v>887.3285146238775</v>
+        <v>960.4588028031553</v>
       </c>
       <c r="H49" t="n">
-        <v>212.252547492157</v>
+        <v>209.4153569261458</v>
       </c>
       <c r="I49" t="n">
-        <v>0.01406261046876454</v>
+        <v>0.0287404785156473</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01752994170999109</v>
+        <v>0.03738647853054497</v>
       </c>
       <c r="K49" t="n">
-        <v>1.536501574687842e-07</v>
+        <v>6.988773364646117e-07</v>
       </c>
       <c r="L49" t="n">
-        <v>2.919534843202627e-07</v>
+        <v>4.1203554146991e-07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>drag_rr_intake_gt_body_wake_split_refuel_on_ar2.toml</t>
+          <t>case_cr_equal_area_refuel_on_ar2_fixed_body_ratio.toml</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 2.0</t>
+          <t>Case CR Equal Area | Refueling | AR 2.0 | Fixed Body Ratio</t>
         </is>
       </c>
       <c r="C50" t="b">
@@ -2612,32 +2612,4256 @@
         </is>
       </c>
       <c r="E50" t="n">
+        <v>18</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3434.692447050633</v>
+      </c>
+      <c r="G50" t="n">
+        <v>882.1582121477563</v>
+      </c>
+      <c r="H50" t="n">
+        <v>190.6988844442939</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.02602246457394107</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.03279898125088031</v>
+      </c>
+      <c r="K50" t="n">
+        <v>5.378893081474694e-07</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3.315673567636725e-07</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>case_cr_equal_area_refuel_on_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Case CR Equal Area | Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C51" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>34</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3786.409651475871</v>
+      </c>
+      <c r="G51" t="n">
+        <v>894.4380023138403</v>
+      </c>
+      <c r="H51" t="n">
+        <v>195.3869903985822</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.02895245497067577</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.03738647661999939</v>
+      </c>
+      <c r="K51" t="n">
+        <v>6.988926843056896e-07</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.837127067872151e-07</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>case_cr_equal_area_refuel_on_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Case CR Equal Area | Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C52" t="b">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>56</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3797.433293979345</v>
+      </c>
+      <c r="G52" t="n">
+        <v>910.0423835915682</v>
+      </c>
+      <c r="H52" t="n">
+        <v>198.9566696531181</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.0289021339009542</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.03738647834003385</v>
+      </c>
+      <c r="K52" t="n">
+        <v>6.988789943802647e-07</v>
+      </c>
+      <c r="L52" t="n">
+        <v>3.904069779521566e-07</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>case_cr_equal_area_refuel_on_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Case CR Equal Area | Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C53" t="b">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>13</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3391.892129364377</v>
+      </c>
+      <c r="G53" t="n">
+        <v>891.4279594615971</v>
+      </c>
+      <c r="H53" t="n">
+        <v>191.6190424514089</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.0255335993500978</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.03210565584999761</v>
+      </c>
+      <c r="K53" t="n">
+        <v>5.155354113117917e-07</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3.279832753593938e-07</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>case_cr_equal_area_refuel_on_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Case CR Equal Area | Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C54" t="b">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>37</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3795.19937695613</v>
+      </c>
+      <c r="G54" t="n">
+        <v>906.8687210169721</v>
+      </c>
+      <c r="H54" t="n">
+        <v>197.0256156929255</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.02891174893948353</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.03738647736392232</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6.98886673460632e-07</v>
+      </c>
+      <c r="L54" t="n">
+        <v>3.890454937070062e-07</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>case_cr_equal_area_refuel_on_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Case CR Equal Area | Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C55" t="b">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>62</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3811.03610208999</v>
+      </c>
+      <c r="G55" t="n">
+        <v>929.2600485041602</v>
+      </c>
+      <c r="H55" t="n">
+        <v>201.6360095053495</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.02883962970286946</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.0373864784266087</v>
+      </c>
+      <c r="K55" t="n">
+        <v>6.988782624107332e-07</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3.986513249191893e-07</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>case_cr_equal_area_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Case CR Equal Area | No Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C56" t="b">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>12</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>840.9134493144896</v>
+      </c>
+      <c r="H56" t="n">
+        <v>157.2715149365926</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.03192605774321647</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.03738647712768955</v>
+      </c>
+      <c r="K56" t="n">
+        <v>6.988954353177945e-07</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C57" t="b">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>872.9711298886225</v>
+      </c>
+      <c r="H57" t="n">
+        <v>174.8621686701721</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.04337046152529268</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.05530396684266069</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1.529264374267057e-06</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C58" t="b">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>12</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>865.2755014245039</v>
+      </c>
+      <c r="H58" t="n">
+        <v>177.0307166627742</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.0319337655730393</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.03738647893593702</v>
+      </c>
+      <c r="K58" t="n">
+        <v>6.988744036968274e-07</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C59" t="b">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>845.2261755508121</v>
+      </c>
+      <c r="H59" t="n">
+        <v>160.3080978258472</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.03192736497339169</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.03738647692267338</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6.988967945556654e-07</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C60" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>12</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>855.8045669043574</v>
+      </c>
+      <c r="H60" t="n">
+        <v>172.1646396847524</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.04502592698860284</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.05828194253928824</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1.698392413076448e-06</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C61" t="b">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>12</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>850.0595438025169</v>
+      </c>
+      <c r="H61" t="n">
+        <v>175.421277330283</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.0319330956336888</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.03738647893441586</v>
+      </c>
+      <c r="K61" t="n">
+        <v>6.988744178633079e-07</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C62" t="b">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>13</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>836.1449750313232</v>
+      </c>
+      <c r="H62" t="n">
+        <v>156.4511889841546</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.03192300297800277</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.03738648594599184</v>
+      </c>
+      <c r="K62" t="n">
+        <v>6.987919589540284e-07</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C63" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>12</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G63" t="n">
+        <v>865.860506681208</v>
+      </c>
+      <c r="H63" t="n">
+        <v>172.7526235885518</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.04465957190975832</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.05761200920299393</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1.659571802202929e-06</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C64" t="b">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>12</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>858.1781206348586</v>
+      </c>
+      <c r="H64" t="n">
+        <v>172.6822701304747</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.0319319541375369</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.03738647893594608</v>
+      </c>
+      <c r="K64" t="n">
+        <v>6.988744036136792e-07</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_refuel_on_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C65" t="b">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>18</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3268.426121747752</v>
+      </c>
+      <c r="G65" t="n">
+        <v>896.270654534981</v>
+      </c>
+      <c r="H65" t="n">
+        <v>194.4454717357742</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.02427778385194725</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.03026727049398047</v>
+      </c>
+      <c r="K65" t="n">
+        <v>4.580554300394313e-07</v>
+      </c>
+      <c r="L65" t="n">
+        <v>3.106400125051643e-07</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_refuel_on_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C66" t="b">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>40</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3803.765262357243</v>
+      </c>
+      <c r="G66" t="n">
+        <v>918.9728560919849</v>
+      </c>
+      <c r="H66" t="n">
+        <v>201.5727192143722</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.02887418939032195</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.03738647751493945</v>
+      </c>
+      <c r="K66" t="n">
+        <v>6.988851692686321e-07</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3.942381217305791e-07</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_refuel_on_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C67" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>77</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3833.119900767944</v>
+      </c>
+      <c r="G67" t="n">
+        <v>960.4588028031553</v>
+      </c>
+      <c r="H67" t="n">
+        <v>209.4153569261458</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.0287404785156473</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.03738647853054497</v>
+      </c>
+      <c r="K67" t="n">
+        <v>6.988773364646117e-07</v>
+      </c>
+      <c r="L67" t="n">
+        <v>4.1203554146991e-07</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_refuel_on_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C68" t="b">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>18</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3434.692447050633</v>
+      </c>
+      <c r="G68" t="n">
+        <v>882.1582121477563</v>
+      </c>
+      <c r="H68" t="n">
+        <v>190.6988844442939</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.02602246457394107</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.03279898125088031</v>
+      </c>
+      <c r="K68" t="n">
+        <v>5.378893081474694e-07</v>
+      </c>
+      <c r="L68" t="n">
+        <v>3.315673567636725e-07</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_refuel_on_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C69" t="b">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>34</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3786.409651475871</v>
+      </c>
+      <c r="G69" t="n">
+        <v>894.4380023138403</v>
+      </c>
+      <c r="H69" t="n">
+        <v>195.3869903985822</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.02895245497067577</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.03738647661999939</v>
+      </c>
+      <c r="K69" t="n">
+        <v>6.988926843056896e-07</v>
+      </c>
+      <c r="L69" t="n">
+        <v>3.837127067872151e-07</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_refuel_on_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C70" t="b">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>56</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3797.433293979345</v>
+      </c>
+      <c r="G70" t="n">
+        <v>910.0423835915682</v>
+      </c>
+      <c r="H70" t="n">
+        <v>198.9566696531181</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.0289021339009542</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.03738647834003385</v>
+      </c>
+      <c r="K70" t="n">
+        <v>6.988789943802647e-07</v>
+      </c>
+      <c r="L70" t="n">
+        <v>3.904069779521566e-07</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_refuel_on_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C71" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>13</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3391.892129364377</v>
+      </c>
+      <c r="G71" t="n">
+        <v>891.4279594615971</v>
+      </c>
+      <c r="H71" t="n">
+        <v>191.6190424514089</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.0255335993500978</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.03210565584999761</v>
+      </c>
+      <c r="K71" t="n">
+        <v>5.155354113117917e-07</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3.279832753593938e-07</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_refuel_on_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C72" t="b">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>37</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3795.19937695613</v>
+      </c>
+      <c r="G72" t="n">
+        <v>906.8687210169721</v>
+      </c>
+      <c r="H72" t="n">
+        <v>197.0256156929255</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.02891174893948353</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.03738647736392232</v>
+      </c>
+      <c r="K72" t="n">
+        <v>6.98886673460632e-07</v>
+      </c>
+      <c r="L72" t="n">
+        <v>3.890454937070062e-07</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_refuel_on_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C73" t="b">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>62</v>
+      </c>
+      <c r="F73" t="n">
+        <v>3811.03610208999</v>
+      </c>
+      <c r="G73" t="n">
+        <v>929.2600485041602</v>
+      </c>
+      <c r="H73" t="n">
+        <v>201.6360095053495</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.02883962970286946</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.0373864784266087</v>
+      </c>
+      <c r="K73" t="n">
+        <v>6.988782624107332e-07</v>
+      </c>
+      <c r="L73" t="n">
+        <v>3.986513249191893e-07</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>case_cr_intake_gt_body_wake_split_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Case CR Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C74" t="b">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>12</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G74" t="n">
+        <v>840.9134493144896</v>
+      </c>
+      <c r="H74" t="n">
+        <v>157.2715149365926</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.03192605774321647</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.03738647712768955</v>
+      </c>
+      <c r="K74" t="n">
+        <v>6.988954353177945e-07</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | No Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C75" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>12</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G75" t="n">
+        <v>872.5783946673973</v>
+      </c>
+      <c r="H75" t="n">
+        <v>174.5450461356472</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.04356174661737805</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.05564177406660649</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1.548003510639641e-06</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | No Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C76" t="b">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>12</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G76" t="n">
+        <v>867.1674965010394</v>
+      </c>
+      <c r="H76" t="n">
+        <v>185.0052630992204</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.03193708286321102</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.03738647893585562</v>
+      </c>
+      <c r="K76" t="n">
+        <v>6.988744043858472e-07</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | No Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C77" t="b">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>16</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G77" t="n">
+        <v>844.8700464595129</v>
+      </c>
+      <c r="H77" t="n">
+        <v>159.8462273484675</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.03192588187755132</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.03738648142506677</v>
+      </c>
+      <c r="K77" t="n">
+        <v>6.988465102082043e-07</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | No Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C78" t="b">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>12</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G78" t="n">
+        <v>855.0190964619071</v>
+      </c>
+      <c r="H78" t="n">
+        <v>171.782751680751</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.04526544228324116</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.05872344965868011</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1.724221769907768e-06</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | No Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C79" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>12</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G79" t="n">
+        <v>850.4709139848488</v>
+      </c>
+      <c r="H79" t="n">
+        <v>183.5644923393014</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.03193648408127597</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.03738647893530581</v>
+      </c>
+      <c r="K79" t="n">
+        <v>6.988744091486327e-07</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | No Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C80" t="b">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
         <v>14</v>
       </c>
-      <c r="F50" t="n">
-        <v>2888.470760927617</v>
-      </c>
-      <c r="G50" t="n">
-        <v>873.8266025004165</v>
-      </c>
-      <c r="H50" t="n">
-        <v>205.8473980682912</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.01608674822264112</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.02027879107625374</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.055986165172611e-07</v>
-      </c>
-      <c r="L50" t="n">
-        <v>3.328351267252224e-07</v>
+      <c r="F80" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G80" t="n">
+        <v>835.7362062792806</v>
+      </c>
+      <c r="H80" t="n">
+        <v>155.9228976662408</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.03192163496494225</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.037386489584092</v>
+      </c>
+      <c r="K80" t="n">
+        <v>6.987481139841763e-07</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | No Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C81" t="b">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>12</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G81" t="n">
+        <v>865.3050952049298</v>
+      </c>
+      <c r="H81" t="n">
+        <v>172.3547806037884</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.04490710210813625</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.05806394767224868</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1.685711009642817e-06</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | No Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C82" t="b">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>12</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G82" t="n">
+        <v>858.5919616166614</v>
+      </c>
+      <c r="H82" t="n">
+        <v>178.7213309582924</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.03193446934406077</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.03738647893594604</v>
+      </c>
+      <c r="K82" t="n">
+        <v>6.988744036140491e-07</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_refuel_on_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C83" t="b">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>16</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3285.790714124137</v>
+      </c>
+      <c r="G83" t="n">
+        <v>896.196886844549</v>
+      </c>
+      <c r="H83" t="n">
+        <v>194.0264652589183</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.02445462456625275</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.03052637567326264</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4.659255626988419e-07</v>
+      </c>
+      <c r="L83" t="n">
+        <v>3.132932227448886e-07</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_refuel_on_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C84" t="b">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>40</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3803.577976827235</v>
+      </c>
+      <c r="G84" t="n">
+        <v>918.7093418348718</v>
+      </c>
+      <c r="H84" t="n">
+        <v>201.4147490142</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.0288749539377946</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.03738647757723683</v>
+      </c>
+      <c r="K84" t="n">
+        <v>6.988847121353431e-07</v>
+      </c>
+      <c r="L84" t="n">
+        <v>3.941250795193633e-07</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_refuel_on_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C85" t="b">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>75</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3830.223829462634</v>
+      </c>
+      <c r="G85" t="n">
+        <v>956.3678456383855</v>
+      </c>
+      <c r="H85" t="n">
+        <v>208.2554563745327</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.02875337351786098</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.03738647854478992</v>
+      </c>
+      <c r="K85" t="n">
+        <v>6.988772534788442e-07</v>
+      </c>
+      <c r="L85" t="n">
+        <v>4.102805385460558e-07</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_refuel_on_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C86" t="b">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>13</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3458.221139024502</v>
+      </c>
+      <c r="G86" t="n">
+        <v>881.8049366350244</v>
+      </c>
+      <c r="H86" t="n">
+        <v>190.218351936344</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.0262417030597465</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.0331281033923171</v>
+      </c>
+      <c r="K86" t="n">
+        <v>5.488596959413225e-07</v>
+      </c>
+      <c r="L86" t="n">
+        <v>3.348558981886755e-07</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_refuel_on_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C87" t="b">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>33</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3785.892558504705</v>
+      </c>
+      <c r="G87" t="n">
+        <v>893.7098696134079</v>
+      </c>
+      <c r="H87" t="n">
+        <v>194.9673963516857</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.02895458680499756</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.03738647675174601</v>
+      </c>
+      <c r="K87" t="n">
+        <v>6.988916821774523e-07</v>
+      </c>
+      <c r="L87" t="n">
+        <v>3.834003386659025e-07</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_refuel_on_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C88" t="b">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>54</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3795.178417005583</v>
+      </c>
+      <c r="G88" t="n">
+        <v>906.8566032022245</v>
+      </c>
+      <c r="H88" t="n">
+        <v>197.7740079593814</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.02891202346750731</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.03738647832111849</v>
+      </c>
+      <c r="K88" t="n">
+        <v>6.988791795466788e-07</v>
+      </c>
+      <c r="L88" t="n">
+        <v>3.89040285408205e-07</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_refuel_on_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C89" t="b">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>13</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3415.463874649765</v>
+      </c>
+      <c r="G89" t="n">
+        <v>891.305533754705</v>
+      </c>
+      <c r="H89" t="n">
+        <v>191.112351900241</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.02575864431788911</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.03244234476716388</v>
+      </c>
+      <c r="K89" t="n">
+        <v>5.263978110265675e-07</v>
+      </c>
+      <c r="L89" t="n">
+        <v>3.314058961618031e-07</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_refuel_on_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C90" t="b">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>37</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3794.800681504332</v>
+      </c>
+      <c r="G90" t="n">
+        <v>906.3045441484394</v>
+      </c>
+      <c r="H90" t="n">
+        <v>196.6573705202692</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.02891341304010663</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.037386477314085</v>
+      </c>
+      <c r="K90" t="n">
+        <v>6.988870975932969e-07</v>
+      </c>
+      <c r="L90" t="n">
+        <v>3.888034509483085e-07</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_refuel_on_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C91" t="b">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>60</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3808.477708006118</v>
+      </c>
+      <c r="G91" t="n">
+        <v>925.6457189460402</v>
+      </c>
+      <c r="H91" t="n">
+        <v>200.3536644227039</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.02885087546863424</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.03738647841885632</v>
+      </c>
+      <c r="K91" t="n">
+        <v>6.988783544054537e-07</v>
+      </c>
+      <c r="L91" t="n">
+        <v>3.971007871879869e-07</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>case_rc_equal_area_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Case RC Equal Area | No Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C92" t="b">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>14</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G92" t="n">
+        <v>840.5328473149505</v>
+      </c>
+      <c r="H92" t="n">
+        <v>156.7149995321637</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.03192432056064698</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.03738648217212238</v>
+      </c>
+      <c r="K92" t="n">
+        <v>6.988364477037139e-07</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C93" t="b">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>12</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G93" t="n">
+        <v>872.5783946673973</v>
+      </c>
+      <c r="H93" t="n">
+        <v>174.5450461356472</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.04356174661737805</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.05564177406660649</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1.548003510639641e-06</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C94" t="b">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>12</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G94" t="n">
+        <v>867.1674965010394</v>
+      </c>
+      <c r="H94" t="n">
+        <v>185.0052630992204</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.03193708286321102</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.03738647893585562</v>
+      </c>
+      <c r="K94" t="n">
+        <v>6.988744043858472e-07</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C95" t="b">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>16</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G95" t="n">
+        <v>844.8700464595129</v>
+      </c>
+      <c r="H95" t="n">
+        <v>159.8462273484675</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.03192588187755132</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.03738648142506677</v>
+      </c>
+      <c r="K95" t="n">
+        <v>6.988465102082043e-07</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C96" t="b">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>12</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G96" t="n">
+        <v>855.0190964619071</v>
+      </c>
+      <c r="H96" t="n">
+        <v>171.782751680751</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.04526544228324116</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.05872344965868011</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1.724221769907768e-06</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C97" t="b">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>12</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G97" t="n">
+        <v>850.4709139848488</v>
+      </c>
+      <c r="H97" t="n">
+        <v>183.5644923393014</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.03193648408127597</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.03738647893530581</v>
+      </c>
+      <c r="K97" t="n">
+        <v>6.988744091486327e-07</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C98" t="b">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>14</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G98" t="n">
+        <v>835.7362062792806</v>
+      </c>
+      <c r="H98" t="n">
+        <v>155.9228976662408</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.03192163496494225</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.037386489584092</v>
+      </c>
+      <c r="K98" t="n">
+        <v>6.987481139841763e-07</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C99" t="b">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>12</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G99" t="n">
+        <v>865.3050952049298</v>
+      </c>
+      <c r="H99" t="n">
+        <v>172.3547806037884</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.04490710210813625</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.05806394767224868</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1.685711009642817e-06</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C100" t="b">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>12</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G100" t="n">
+        <v>858.5919616166614</v>
+      </c>
+      <c r="H100" t="n">
+        <v>178.7213309582924</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.03193446934406077</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.03738647893594604</v>
+      </c>
+      <c r="K100" t="n">
+        <v>6.988744036140491e-07</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_refuel_on_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C101" t="b">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>16</v>
+      </c>
+      <c r="F101" t="n">
+        <v>3285.790714124137</v>
+      </c>
+      <c r="G101" t="n">
+        <v>896.196886844549</v>
+      </c>
+      <c r="H101" t="n">
+        <v>194.0264652589183</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.02445462456625275</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.03052637567326264</v>
+      </c>
+      <c r="K101" t="n">
+        <v>4.659255626988419e-07</v>
+      </c>
+      <c r="L101" t="n">
+        <v>3.132932227448886e-07</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_refuel_on_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C102" t="b">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>40</v>
+      </c>
+      <c r="F102" t="n">
+        <v>3803.577976827235</v>
+      </c>
+      <c r="G102" t="n">
+        <v>918.7093418348718</v>
+      </c>
+      <c r="H102" t="n">
+        <v>201.4147490142</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.0288749539377946</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.03738647757723683</v>
+      </c>
+      <c r="K102" t="n">
+        <v>6.988847121353431e-07</v>
+      </c>
+      <c r="L102" t="n">
+        <v>3.941250795193633e-07</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_refuel_on_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C103" t="b">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>75</v>
+      </c>
+      <c r="F103" t="n">
+        <v>3830.223829462634</v>
+      </c>
+      <c r="G103" t="n">
+        <v>956.3678456383855</v>
+      </c>
+      <c r="H103" t="n">
+        <v>208.2554563745327</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.02875337351786098</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.03738647854478992</v>
+      </c>
+      <c r="K103" t="n">
+        <v>6.988772534788442e-07</v>
+      </c>
+      <c r="L103" t="n">
+        <v>4.102805385460558e-07</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_refuel_on_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>13</v>
+      </c>
+      <c r="F104" t="n">
+        <v>3458.221139024502</v>
+      </c>
+      <c r="G104" t="n">
+        <v>881.8049366350244</v>
+      </c>
+      <c r="H104" t="n">
+        <v>190.218351936344</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.0262417030597465</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.0331281033923171</v>
+      </c>
+      <c r="K104" t="n">
+        <v>5.488596959413225e-07</v>
+      </c>
+      <c r="L104" t="n">
+        <v>3.348558981886755e-07</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_refuel_on_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C105" t="b">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>33</v>
+      </c>
+      <c r="F105" t="n">
+        <v>3785.892558504705</v>
+      </c>
+      <c r="G105" t="n">
+        <v>893.7098696134079</v>
+      </c>
+      <c r="H105" t="n">
+        <v>194.9673963516857</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.02895458680499756</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.03738647675174601</v>
+      </c>
+      <c r="K105" t="n">
+        <v>6.988916821774523e-07</v>
+      </c>
+      <c r="L105" t="n">
+        <v>3.834003386659025e-07</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_refuel_on_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C106" t="b">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>54</v>
+      </c>
+      <c r="F106" t="n">
+        <v>3795.178417005583</v>
+      </c>
+      <c r="G106" t="n">
+        <v>906.8566032022245</v>
+      </c>
+      <c r="H106" t="n">
+        <v>197.7740079593814</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.02891202346750731</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.03738647832111849</v>
+      </c>
+      <c r="K106" t="n">
+        <v>6.988791795466788e-07</v>
+      </c>
+      <c r="L106" t="n">
+        <v>3.89040285408205e-07</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_refuel_on_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C107" t="b">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>13</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3415.463874649765</v>
+      </c>
+      <c r="G107" t="n">
+        <v>891.305533754705</v>
+      </c>
+      <c r="H107" t="n">
+        <v>191.112351900241</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.02575864431788911</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.03244234476716388</v>
+      </c>
+      <c r="K107" t="n">
+        <v>5.263978110265675e-07</v>
+      </c>
+      <c r="L107" t="n">
+        <v>3.314058961618031e-07</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_refuel_on_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C108" t="b">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>37</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3794.800681504332</v>
+      </c>
+      <c r="G108" t="n">
+        <v>906.3045441484394</v>
+      </c>
+      <c r="H108" t="n">
+        <v>196.6573705202692</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.02891341304010663</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.037386477314085</v>
+      </c>
+      <c r="K108" t="n">
+        <v>6.988870975932969e-07</v>
+      </c>
+      <c r="L108" t="n">
+        <v>3.888034509483085e-07</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_refuel_on_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>60</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3808.477708006118</v>
+      </c>
+      <c r="G109" t="n">
+        <v>925.6457189460402</v>
+      </c>
+      <c r="H109" t="n">
+        <v>200.3536644227039</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.02885087546863424</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.03738647841885632</v>
+      </c>
+      <c r="K109" t="n">
+        <v>6.988783544054537e-07</v>
+      </c>
+      <c r="L109" t="n">
+        <v>3.971007871879869e-07</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>case_rc_intake_gt_body_wake_split_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Case RC Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C110" t="b">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>14</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G110" t="n">
+        <v>840.5328473149505</v>
+      </c>
+      <c r="H110" t="n">
+        <v>156.7149995321637</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.03192432056064698</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.03738648217212238</v>
+      </c>
+      <c r="K110" t="n">
+        <v>6.988364477037139e-07</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | No Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C111" t="b">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>12</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G111" t="n">
+        <v>873.8220562012771</v>
+      </c>
+      <c r="H111" t="n">
+        <v>175.5481317146771</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.04295978070347077</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.05458398282249579</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1.489705590383257e-06</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | No Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C112" t="b">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>12</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G112" t="n">
+        <v>867.0459438302391</v>
+      </c>
+      <c r="H112" t="n">
+        <v>180.9683751456291</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.03193540432795278</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.03738647893594074</v>
+      </c>
+      <c r="K112" t="n">
+        <v>6.988744036608635e-07</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | No Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C113" t="b">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>16</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G113" t="n">
+        <v>846.0281234448807</v>
+      </c>
+      <c r="H113" t="n">
+        <v>161.3208824265753</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.03192784780403839</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.03738647670181971</v>
+      </c>
+      <c r="K113" t="n">
+        <v>6.988989476489119e-07</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | No Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C114" t="b">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>12</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G114" t="n">
+        <v>857.5064195296667</v>
+      </c>
+      <c r="H114" t="n">
+        <v>172.9905313995028</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.04451225967039768</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.05734442603621422</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1.644191598711422e-06</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | No Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C115" t="b">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>12</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G115" t="n">
+        <v>852.0165242996377</v>
+      </c>
+      <c r="H115" t="n">
+        <v>179.5001813624868</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.03193479355534876</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.03738647893552041</v>
+      </c>
+      <c r="K115" t="n">
+        <v>6.988744074259766e-07</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | No Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C116" t="b">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>13</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G116" t="n">
+        <v>837.0763848928102</v>
+      </c>
+      <c r="H116" t="n">
+        <v>157.6108183770769</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.03192428520091444</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.0373864834238363</v>
+      </c>
+      <c r="K116" t="n">
+        <v>6.988224871888939e-07</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | No Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C117" t="b">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>12</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G117" t="n">
+        <v>867.0638982131443</v>
+      </c>
+      <c r="H117" t="n">
+        <v>173.6130735295342</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.04412903231092109</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.05665304087567893</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1.604783520230673e-06</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | No Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C118" t="b">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>12</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G118" t="n">
+        <v>859.6903005798379</v>
+      </c>
+      <c r="H118" t="n">
+        <v>176.0292595132461</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.03193334855399056</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.037386478935946</v>
+      </c>
+      <c r="K118" t="n">
+        <v>6.988744036144234e-07</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_refuel_on_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>16</v>
+      </c>
+      <c r="F119" t="n">
+        <v>3231.511574621092</v>
+      </c>
+      <c r="G119" t="n">
+        <v>896.4435032001951</v>
+      </c>
+      <c r="H119" t="n">
+        <v>195.3587451363677</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.02389666383403948</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.02971151424051509</v>
+      </c>
+      <c r="K119" t="n">
+        <v>4.413825693532733e-07</v>
+      </c>
+      <c r="L119" t="n">
+        <v>3.049418074640082e-07</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_refuel_on_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C120" t="b">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>42</v>
+      </c>
+      <c r="F120" t="n">
+        <v>3805.735913156993</v>
+      </c>
+      <c r="G120" t="n">
+        <v>921.7605436255121</v>
+      </c>
+      <c r="H120" t="n">
+        <v>203.2066988936152</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.02886587870591678</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.03738647772385392</v>
+      </c>
+      <c r="K120" t="n">
+        <v>6.988834995872885e-07</v>
+      </c>
+      <c r="L120" t="n">
+        <v>3.954340511820758e-07</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_refuel_on_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C121" t="b">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>83</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3839.921828636679</v>
+      </c>
+      <c r="G121" t="n">
+        <v>970.0683634867983</v>
+      </c>
+      <c r="H121" t="n">
+        <v>212.0069796671731</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.02871008811923249</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.03738647857695084</v>
+      </c>
+      <c r="K121" t="n">
+        <v>6.988769638071419e-07</v>
+      </c>
+      <c r="L121" t="n">
+        <v>4.16158039069122e-07</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_refuel_on_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C122" t="b">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>13</v>
+      </c>
+      <c r="F122" t="n">
+        <v>3385.463160841294</v>
+      </c>
+      <c r="G122" t="n">
+        <v>882.9557795745104</v>
+      </c>
+      <c r="H122" t="n">
+        <v>191.757675517318</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.02554615205291598</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.032088057033665</v>
+      </c>
+      <c r="K122" t="n">
+        <v>5.149486004384839e-07</v>
+      </c>
+      <c r="L122" t="n">
+        <v>3.246739832439463e-07</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_refuel_on_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C123" t="b">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>36</v>
+      </c>
+      <c r="F123" t="n">
+        <v>3788.838367211915</v>
+      </c>
+      <c r="G123" t="n">
+        <v>897.8758219038389</v>
+      </c>
+      <c r="H123" t="n">
+        <v>197.3096667154662</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.02894209813543675</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.03738647696882342</v>
+      </c>
+      <c r="K123" t="n">
+        <v>6.988897217514124e-07</v>
+      </c>
+      <c r="L123" t="n">
+        <v>3.851875270126043e-07</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_refuel_on_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C124" t="b">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>60</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3802.725724396877</v>
+      </c>
+      <c r="G124" t="n">
+        <v>917.5196680389222</v>
+      </c>
+      <c r="H124" t="n">
+        <v>201.5833622063226</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.02887883256770381</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.0373864783835151</v>
+      </c>
+      <c r="K124" t="n">
+        <v>6.988785888601303e-07</v>
+      </c>
+      <c r="L124" t="n">
+        <v>3.936147181937927e-07</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_refuel_on_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C125" t="b">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>18</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3341.768385232405</v>
+      </c>
+      <c r="G125" t="n">
+        <v>891.7106356347534</v>
+      </c>
+      <c r="H125" t="n">
+        <v>192.7228406550365</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.02504966704988687</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.03138629956746229</v>
+      </c>
+      <c r="K125" t="n">
+        <v>4.92552123020151e-07</v>
+      </c>
+      <c r="L125" t="n">
+        <v>3.205904203211979e-07</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_refuel_on_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C126" t="b">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>39</v>
+      </c>
+      <c r="F126" t="n">
+        <v>3797.444075248959</v>
+      </c>
+      <c r="G126" t="n">
+        <v>910.0428486386528</v>
+      </c>
+      <c r="H126" t="n">
+        <v>199.0337561501823</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.02890239031464446</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.03738647751894759</v>
+      </c>
+      <c r="K126" t="n">
+        <v>6.988853200116329e-07</v>
+      </c>
+      <c r="L126" t="n">
+        <v>3.904071860184753e-07</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_refuel_on_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C127" t="b">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>67</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3817.075478032279</v>
+      </c>
+      <c r="G127" t="n">
+        <v>937.7926798890639</v>
+      </c>
+      <c r="H127" t="n">
+        <v>204.4920529609864</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.02881296664413517</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.03738647848349141</v>
+      </c>
+      <c r="K127" t="n">
+        <v>6.988777709595788e-07</v>
+      </c>
+      <c r="L127" t="n">
+        <v>4.023118172825397e-07</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>case_rr_equal_area_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Case RR Equal Area | No Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C128" t="b">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>13</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G128" t="n">
+        <v>841.7810920495382</v>
+      </c>
+      <c r="H128" t="n">
+        <v>158.494649604926</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.0319269854923802</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.03738647569594481</v>
+      </c>
+      <c r="K128" t="n">
+        <v>6.989113869515107e-07</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C129" t="b">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>12</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G129" t="n">
+        <v>873.8220562012771</v>
+      </c>
+      <c r="H129" t="n">
+        <v>175.5481317146771</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.04295978070347077</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.05458398282249579</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1.489705590383257e-06</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C130" t="b">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>12</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G130" t="n">
+        <v>867.0459438302391</v>
+      </c>
+      <c r="H130" t="n">
+        <v>180.9683751456291</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.03193540432795278</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.03738647893594074</v>
+      </c>
+      <c r="K130" t="n">
+        <v>6.988744036608635e-07</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C131" t="b">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>16</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G131" t="n">
+        <v>846.0281234448807</v>
+      </c>
+      <c r="H131" t="n">
+        <v>161.3208824265753</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.03192784780403839</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.03738647670181971</v>
+      </c>
+      <c r="K131" t="n">
+        <v>6.988989476489119e-07</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C132" t="b">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>12</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G132" t="n">
+        <v>857.5064195296667</v>
+      </c>
+      <c r="H132" t="n">
+        <v>172.9905313995028</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.04451225967039768</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.05734442603621422</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1.644191598711422e-06</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C133" t="b">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>12</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G133" t="n">
+        <v>852.0165242996377</v>
+      </c>
+      <c r="H133" t="n">
+        <v>179.5001813624868</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.03193479355534876</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.03738647893552041</v>
+      </c>
+      <c r="K133" t="n">
+        <v>6.988744074259766e-07</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C134" t="b">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>13</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G134" t="n">
+        <v>837.0763848928102</v>
+      </c>
+      <c r="H134" t="n">
+        <v>157.6108183770769</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.03192428520091444</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.0373864834238363</v>
+      </c>
+      <c r="K134" t="n">
+        <v>6.988224871888939e-07</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C135" t="b">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>12</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G135" t="n">
+        <v>867.0638982131443</v>
+      </c>
+      <c r="H135" t="n">
+        <v>173.6130735295342</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.04412903231092109</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.05665304087567893</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1.604783520230673e-06</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C136" t="b">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>12</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G136" t="n">
+        <v>859.6903005798379</v>
+      </c>
+      <c r="H136" t="n">
+        <v>176.0292595132461</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.03193334855399056</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.037386478935946</v>
+      </c>
+      <c r="K136" t="n">
+        <v>6.988744036144234e-07</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_refuel_on_ar05_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 0.5 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C137" t="b">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>16</v>
+      </c>
+      <c r="F137" t="n">
+        <v>3231.511574621092</v>
+      </c>
+      <c r="G137" t="n">
+        <v>896.4435032001951</v>
+      </c>
+      <c r="H137" t="n">
+        <v>195.3587451363677</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.02389666383403948</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.02971151424051509</v>
+      </c>
+      <c r="K137" t="n">
+        <v>4.413825693532733e-07</v>
+      </c>
+      <c r="L137" t="n">
+        <v>3.049418074640082e-07</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_refuel_on_ar05_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 0.5 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C138" t="b">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>42</v>
+      </c>
+      <c r="F138" t="n">
+        <v>3805.735913156993</v>
+      </c>
+      <c r="G138" t="n">
+        <v>921.7605436255121</v>
+      </c>
+      <c r="H138" t="n">
+        <v>203.2066988936152</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.02886587870591678</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.03738647772385392</v>
+      </c>
+      <c r="K138" t="n">
+        <v>6.988834995872885e-07</v>
+      </c>
+      <c r="L138" t="n">
+        <v>3.954340511820758e-07</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_refuel_on_ar05_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 0.5 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C139" t="b">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>83</v>
+      </c>
+      <c r="F139" t="n">
+        <v>3839.921828636679</v>
+      </c>
+      <c r="G139" t="n">
+        <v>970.0683634867983</v>
+      </c>
+      <c r="H139" t="n">
+        <v>212.0069796671731</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.02871008811923249</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.03738647857695084</v>
+      </c>
+      <c r="K139" t="n">
+        <v>6.988769638071419e-07</v>
+      </c>
+      <c r="L139" t="n">
+        <v>4.16158039069122e-07</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_refuel_on_ar2_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 2.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C140" t="b">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>13</v>
+      </c>
+      <c r="F140" t="n">
+        <v>3385.463160841294</v>
+      </c>
+      <c r="G140" t="n">
+        <v>882.9557795745104</v>
+      </c>
+      <c r="H140" t="n">
+        <v>191.757675517318</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.02554615205291598</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.032088057033665</v>
+      </c>
+      <c r="K140" t="n">
+        <v>5.149486004384839e-07</v>
+      </c>
+      <c r="L140" t="n">
+        <v>3.246739832439463e-07</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_refuel_on_ar2_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 2.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C141" t="b">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>36</v>
+      </c>
+      <c r="F141" t="n">
+        <v>3788.838367211915</v>
+      </c>
+      <c r="G141" t="n">
+        <v>897.8758219038389</v>
+      </c>
+      <c r="H141" t="n">
+        <v>197.3096667154662</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.02894209813543675</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.03738647696882342</v>
+      </c>
+      <c r="K141" t="n">
+        <v>6.988897217514124e-07</v>
+      </c>
+      <c r="L141" t="n">
+        <v>3.851875270126043e-07</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_refuel_on_ar2_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 2.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C142" t="b">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>60</v>
+      </c>
+      <c r="F142" t="n">
+        <v>3802.725724396877</v>
+      </c>
+      <c r="G142" t="n">
+        <v>917.5196680389222</v>
+      </c>
+      <c r="H142" t="n">
+        <v>201.5833622063226</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.02887883256770381</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.0373864783835151</v>
+      </c>
+      <c r="K142" t="n">
+        <v>6.988785888601303e-07</v>
+      </c>
+      <c r="L142" t="n">
+        <v>3.936147181937927e-07</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_refuel_on_fixed_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 1.0 | Fixed Body Ratio</t>
+        </is>
+      </c>
+      <c r="C143" t="b">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>18</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3341.768385232405</v>
+      </c>
+      <c r="G143" t="n">
+        <v>891.7106356347534</v>
+      </c>
+      <c r="H143" t="n">
+        <v>192.7228406550365</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.02504966704988687</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.03138629956746229</v>
+      </c>
+      <c r="K143" t="n">
+        <v>4.92552123020151e-07</v>
+      </c>
+      <c r="L143" t="n">
+        <v>3.205904203211979e-07</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_refuel_on_free_intake.toml</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 1.0 | Free Intake</t>
+        </is>
+      </c>
+      <c r="C144" t="b">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>39</v>
+      </c>
+      <c r="F144" t="n">
+        <v>3797.444075248959</v>
+      </c>
+      <c r="G144" t="n">
+        <v>910.0428486386528</v>
+      </c>
+      <c r="H144" t="n">
+        <v>199.0337561501823</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.02890239031464446</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0.03738647751894759</v>
+      </c>
+      <c r="K144" t="n">
+        <v>6.988853200116329e-07</v>
+      </c>
+      <c r="L144" t="n">
+        <v>3.904071860184753e-07</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_refuel_on_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C145" t="b">
+        <v>1</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>67</v>
+      </c>
+      <c r="F145" t="n">
+        <v>3817.075478032279</v>
+      </c>
+      <c r="G145" t="n">
+        <v>937.7926798890639</v>
+      </c>
+      <c r="H145" t="n">
+        <v>204.4920529609864</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.02881296664413517</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.03738647848349141</v>
+      </c>
+      <c r="K145" t="n">
+        <v>6.988777709595788e-07</v>
+      </c>
+      <c r="L145" t="n">
+        <v>4.023118172825397e-07</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>case_rr_intake_gt_body_wake_split_variable_body_ratio.toml</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Case RR Intake&gt;Body Wake Split | No Refueling | AR 1.0 | Variable Body Ratio</t>
+        </is>
+      </c>
+      <c r="C146" t="b">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Converged</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>13</v>
+      </c>
+      <c r="F146" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G146" t="n">
+        <v>841.7810920495382</v>
+      </c>
+      <c r="H146" t="n">
+        <v>158.494649604926</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.0319269854923802</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.03738647569594481</v>
+      </c>
+      <c r="K146" t="n">
+        <v>6.989113869515107e-07</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L50"/>
+  <autoFilter ref="A1:L146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>